--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>68.41380070771018</v>
+        <v>11.1172426150029</v>
       </c>
       <c r="D2" t="n">
-        <v>51.09511444168239</v>
+        <v>8.302956096773389</v>
       </c>
       <c r="E2" t="n">
-        <v>11.42382144591866</v>
+        <v>1.856370984961782</v>
       </c>
       <c r="F2" t="n">
-        <v>13.12393547623286</v>
+        <v>2.132639514887841</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.05469300489622</v>
+        <v>6.508887613295635</v>
       </c>
       <c r="D3" t="n">
-        <v>9.430924284462792</v>
+        <v>1.532525196225204</v>
       </c>
       <c r="E3" t="n">
-        <v>11.42382144591866</v>
+        <v>1.856370984961782</v>
       </c>
       <c r="F3" t="n">
-        <v>13.12393547623286</v>
+        <v>2.132639514887841</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.4416168917742</v>
+        <v>6.246762744913308</v>
       </c>
       <c r="D4" t="n">
-        <v>39.20467776395672</v>
+        <v>6.370760136642968</v>
       </c>
       <c r="E4" t="n">
-        <v>11.42382144591866</v>
+        <v>1.856370984961782</v>
       </c>
       <c r="F4" t="n">
-        <v>13.12393547623286</v>
+        <v>2.132639514887841</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.52179120032735</v>
+        <v>5.122291070053194</v>
       </c>
       <c r="D5" t="n">
-        <v>31.38850372800597</v>
+        <v>5.10063185580097</v>
       </c>
       <c r="E5" t="n">
-        <v>11.42382144591866</v>
+        <v>1.856370984961782</v>
       </c>
       <c r="F5" t="n">
-        <v>13.12393547623286</v>
+        <v>2.132639514887841</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.95015859858167</v>
+        <v>6.329400772269521</v>
       </c>
       <c r="D6" t="n">
-        <v>37.96249636856017</v>
+        <v>6.168905659891028</v>
       </c>
       <c r="E6" t="n">
-        <v>11.42382144591866</v>
+        <v>1.856370984961782</v>
       </c>
       <c r="F6" t="n">
-        <v>13.12393547623286</v>
+        <v>2.132639514887841</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>48.68659105000512</v>
+        <v>7.911571045625832</v>
       </c>
       <c r="D7" t="n">
-        <v>47.98112594637988</v>
+        <v>7.79693296628673</v>
       </c>
       <c r="E7" t="n">
-        <v>11.42382144591866</v>
+        <v>1.856370984961782</v>
       </c>
       <c r="F7" t="n">
-        <v>13.12393547623286</v>
+        <v>2.132639514887841</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>61.56000808236524</v>
+        <v>10.00350131338435</v>
       </c>
       <c r="D8" t="n">
-        <v>61.33931653144663</v>
+        <v>9.967638936360077</v>
       </c>
       <c r="E8" t="n">
-        <v>11.42382144591866</v>
+        <v>1.856370984961782</v>
       </c>
       <c r="F8" t="n">
-        <v>13.12393547623286</v>
+        <v>2.132639514887841</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.67100359293745</v>
+        <v>6.446538083852335</v>
       </c>
       <c r="D9" t="n">
-        <v>38.89824892181817</v>
+        <v>6.320965449795453</v>
       </c>
       <c r="E9" t="n">
-        <v>11.42382144591866</v>
+        <v>1.856370984961782</v>
       </c>
       <c r="F9" t="n">
-        <v>13.12393547623286</v>
+        <v>2.132639514887841</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>53.41053812356169</v>
+        <v>8.679212445078775</v>
       </c>
       <c r="D10" t="n">
-        <v>52.60045086766749</v>
+        <v>8.547573265995968</v>
       </c>
       <c r="E10" t="n">
-        <v>11.42382144591866</v>
+        <v>1.856370984961782</v>
       </c>
       <c r="F10" t="n">
-        <v>13.12393547623286</v>
+        <v>2.132639514887841</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>38.36915760057865</v>
+        <v>6.23498811009403</v>
       </c>
       <c r="D11" t="n">
-        <v>37.54481902379842</v>
+        <v>6.101033091367245</v>
       </c>
       <c r="E11" t="n">
-        <v>11.42382144591866</v>
+        <v>1.856370984961782</v>
       </c>
       <c r="F11" t="n">
-        <v>13.12393547623286</v>
+        <v>2.132639514887841</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.70348731059261</v>
+        <v>5.8018166879713</v>
       </c>
       <c r="D12" t="n">
-        <v>34.91613444646051</v>
+        <v>5.673871847549833</v>
       </c>
       <c r="E12" t="n">
-        <v>11.42382144591866</v>
+        <v>1.856370984961782</v>
       </c>
       <c r="F12" t="n">
-        <v>13.12393547623286</v>
+        <v>2.132639514887841</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>60.43063747822735</v>
+        <v>9.819978590211944</v>
       </c>
       <c r="D13" t="n">
-        <v>59.60357779860428</v>
+        <v>9.685581392273196</v>
       </c>
       <c r="E13" t="n">
-        <v>11.42382144591866</v>
+        <v>1.856370984961782</v>
       </c>
       <c r="F13" t="n">
-        <v>13.12393547623286</v>
+        <v>2.132639514887841</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>32.12606398482277</v>
+        <v>5.2204853975337</v>
       </c>
       <c r="D14" t="n">
-        <v>31.81578164974432</v>
+        <v>5.170064518083453</v>
       </c>
       <c r="E14" t="n">
-        <v>11.42382144591866</v>
+        <v>1.856370984961782</v>
       </c>
       <c r="F14" t="n">
-        <v>13.12393547623286</v>
+        <v>2.132639514887841</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>44.31493681835826</v>
+        <v>7.201177232983218</v>
       </c>
       <c r="D15" t="n">
-        <v>43.9404143132135</v>
+        <v>7.140317325897194</v>
       </c>
       <c r="E15" t="n">
-        <v>11.42382144591866</v>
+        <v>1.856370984961782</v>
       </c>
       <c r="F15" t="n">
-        <v>13.12393547623286</v>
+        <v>2.132639514887841</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>63.97402412351384</v>
+        <v>10.395778920071</v>
       </c>
       <c r="D16" t="n">
-        <v>63.18173058335672</v>
+        <v>10.26703121979547</v>
       </c>
       <c r="E16" t="n">
-        <v>11.42382144591866</v>
+        <v>1.856370984961782</v>
       </c>
       <c r="F16" t="n">
-        <v>13.12393547623286</v>
+        <v>2.132639514887841</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>47.30581700044307</v>
+        <v>7.687195262571999</v>
       </c>
       <c r="D17" t="n">
-        <v>46.81981885682627</v>
+        <v>7.608220564234269</v>
       </c>
       <c r="E17" t="n">
-        <v>11.42382144591866</v>
+        <v>1.856370984961782</v>
       </c>
       <c r="F17" t="n">
-        <v>13.12393547623286</v>
+        <v>2.132639514887841</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
